--- a/spec-tech/ig/StructureDefinition-xdmDocumentEntry.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:32:10+00:00</t>
+    <t>2026-07-23T16:03:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -433,7 +433,7 @@
 </t>
   </si>
   <si>
-    <t>Cette métadonnée représente l’identifiant du patient, en l’occurrence, le matricule INS (NIR ou NIA) du patient lorsque celui-ci est qualifié.</t>
+    <t>Cette métadonnée contient l'identifiant du patient tel que connu par les interlocuteurs prenant part à l'échange. Le matricule INS (NIR ou NIA) du patient doit être utilisé en priorité. À défaut de disponibilité de l'INS, un autre identifiant (ex: IPP du système émetteur) peut être utilisé.</t>
   </si>
   <si>
     <t>xdmDocumentEntry.uniqueId</t>

--- a/spec-tech/ig/StructureDefinition-xdmDocumentEntry.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:03:49+00:00</t>
+    <t>2026-07-23T16:11:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmDocumentEntry.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:11:23+00:00</t>
+    <t>2026-07-27T13:36:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmDocumentEntry.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T13:36:25+00:00</t>
+    <t>2026-07-30T09:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmDocumentEntry.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:32:03+00:00</t>
+    <t>2026-07-30T15:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmDocumentEntry.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmDocumentEntry.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="190">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:04:16+00:00</t>
+    <t>2026-08-07T08:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -291,7 +291,7 @@
     <t>xdmDocumentEntry.availabilityStatus</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
+    <t xml:space="preserve">code
 </t>
   </si>
   <si>
@@ -326,6 +326,16 @@
     <t>Cette métadonnée correspond à la taille du document déposé.</t>
   </si>
   <si>
+    <t>xdmDocumentEntry.creationTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Cette métadonnée représente la date et l’heure de la création du document.</t>
+  </si>
+  <si>
     <t>xdmDocumentEntry.languageCode</t>
   </si>
   <si>
@@ -371,10 +381,6 @@
     <t>xdmDocumentEntry.serviceStartTime</t>
   </si>
   <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
     <t>Cette métadonnée représente la date de début de l'acte de référence.</t>
   </si>
   <si>
@@ -404,7 +410,7 @@
     <t>Cette métadonnée contient les traits d'identité du patient concerné par le document, connus par le producteur du document.</t>
   </si>
   <si>
-    <t>xdmDocumentEntry.URI</t>
+    <t>xdmDocumentEntry.uri</t>
   </si>
   <si>
     <t xml:space="preserve">uri
@@ -414,6 +420,12 @@
     <t>Cette métadonnée n'est exploitée que par la transaction XDM 'Distribute document set on media ITI-32'</t>
   </si>
   <si>
+    <t>xdmDocumentEntry.documentAvailability</t>
+  </si>
+  <si>
+    <t>Cette métadonnée représente l’accessibilité du document en indiquant si celui-ci est accessible en ligne ou non</t>
+  </si>
+  <si>
     <t>xdmDocumentEntry.title</t>
   </si>
   <si>
@@ -424,6 +436,12 @@
   </si>
   <si>
     <t>Cette métadonnée contient le commentaire associé au document.</t>
+  </si>
+  <si>
+    <t>xdmDocumentEntry.version</t>
+  </si>
+  <si>
+    <t>Cette métadonnée représente le numéro de version de la fiche d’un document.  La valeur de la métadonnée version est égale à 1 pour la première version de la fiche.</t>
   </si>
   <si>
     <t>xdmDocumentEntry.patientID</t>
@@ -449,43 +467,62 @@
     <t>xdmDocumentEntry.class</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/xdmCode
+</t>
+  </si>
+  <si>
     <t>class représente la classe du document (compte rendu, imagerie médicale, traitement, certificat, etc.).</t>
   </si>
   <si>
-    <t>class est constitué des attributs : 
-- **classCode**
-- **classCodeDisplayName**
-- **codingScheme***
-**classCode**
-- Type : Non contraint
-- Contenu : Les valeurs possibles doivent être un code provenant du jeu de valeurs mis à disposition par le projet (exemple : JDV_J57_ClassCode_DMP). En l’absence de spécifications complémentaires, le JDV_J06_XdsClassCode_CISIS peut être utilisé. 
-- Source : En fonction de l’interface fournie (ex. paramétrage fixe ou choix dans un menu déroulant). 
-**classCodeDisplayName**
-- Type : Non contraint
-- Contenu : L’intitulé de la classe de document correspond au libellé associé au code de **classCode**.
-- Source : En fonction de l’interface fournie (ex. paramétrage fixe ou choix dans un menu déroulant). 
-**codingScheme**
-- Type : OID
-- Le code système de la classe de document correspond à l’OID associé au code de classCode. 
-- Source : En fonction de l’interface fournie (ex. paramétrage fixe ou choix dans un menu déroulant).</t>
-  </si>
-  <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J06-XdsClassCode-CISIS/FHIR/JDV-J06-XdsClassCode-CISIS|20230922120000</t>
   </si>
   <si>
     <t>code@code (classCode est déduit de typeCode selon la table de correspondance entre ces deux métadonnées référencée dans les Nomenclatures des Objets de Santé (NOS) : ASS_X04-CorrespondanceType-Classe)</t>
   </si>
   <si>
+    <t>xdmDocumentEntry.class.code</t>
+  </si>
+  <si>
+    <t>ClassCode de la classe du document.</t>
+  </si>
+  <si>
+    <t>Les valeurs possibles doivent être un code provenant du jeu de valeurs mis à disposition par le projet (exemple : JDV_J57_ClassCode_DMP). En l'absence de spécifications complémentaires, le JDV_J06_XdsClassCode_CISIS peut être utilisé.</t>
+  </si>
+  <si>
+    <t>xdmCode.code</t>
+  </si>
+  <si>
+    <t>xdmDocumentEntry.class.displayName</t>
+  </si>
+  <si>
+    <t>Libellé associé au classCode.</t>
+  </si>
+  <si>
+    <t>Libellé associé au code.</t>
+  </si>
+  <si>
+    <t>xdmCode.displayName</t>
+  </si>
+  <si>
+    <t>xdmDocumentEntry.class.codingScheme</t>
+  </si>
+  <si>
+    <t>OID du système de codage associé au code classCode.</t>
+  </si>
+  <si>
+    <t>OID du système de codage.</t>
+  </si>
+  <si>
+    <t>xdmCode.codingScheme</t>
+  </si>
+  <si>
     <t>xdmDocumentEntry.confidentiality</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>Métadonnée contenant les informations définissant le niveau de confidentialité d'un document déposé dans l'entrepôt. Dans le cadre de la mise en œuvre du masquage et de la non-visibilité, ces métadonnées sont utilisées pour rendre inaccessible un document à l'utilisateur</t>
-  </si>
-  <si>
-    <t>**Confidentiality Code**</t>
+    <t>Métadonnée contenant les informations définissant le niveau de confidentialité d'un document déposé dans l'entrepôt. Dans le cadre de la mise en œuvre du masquage et de la non-visibilité, ces métadonnées sont utilisées pour rendre inaccessible un document à l'utilisateur.</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J58-ConfidentialityCode-DMP/FHIR/JDV-J58-ConfidentialityCode-DMP|20200424120000</t>
@@ -494,112 +531,74 @@
     <t>xdmDocumentEntry.eventCodeList</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/xdmEventCode
+    <t>Cette métadonnée contient les codes, libellés et codes système représentant :  -un évènement documenté (acte, traitement, diagnostic, etc…), -une modalité d'acquisition (contexte imagerie), -une région anatomique (contexte imagerie).</t>
+  </si>
+  <si>
+    <t>xdmDocumentEntry.format</t>
+  </si>
+  <si>
+    <t>Métadonnée contenant les informations définissant le format du document. Il précise les spécifications techniques auxquelles il est conforme</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J10-XdsFormatCode-CISIS/FHIR/JDV-J10-XdsFormatCode-CISIS|20260629120000</t>
+  </si>
+  <si>
+    <t>xdmDocumentEntry.format.code</t>
+  </si>
+  <si>
+    <t>code identifiant le format du document et les spécifications auxquelles il est conforme. Fixé à urn:asipSante:modelesHorsProfils:2011 (Document non référencé IHE ou CI-SIS) pour les documents au format propriétaire.</t>
+  </si>
+  <si>
+    <t>Code de la valeur.</t>
+  </si>
+  <si>
+    <t>xdmDocumentEntry.format.displayName</t>
+  </si>
+  <si>
+    <t>xdmDocumentEntry.format.codingScheme</t>
+  </si>
+  <si>
+    <t>xdmDocumentEntry.healthcareFacilityTypeCode</t>
+  </si>
+  <si>
+    <t>Secteur d'activité lié à la prise en charge de la personne, en lien avec le document produit.</t>
+  </si>
+  <si>
+    <t>Healthcare Facility Type Code**</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J02-XdsHealthcareFacilityTypeCode-CISIS/FHIR/JDV-J02-XdsHealthcareFacilityTypeCode-CISIS|20260223120000</t>
+  </si>
+  <si>
+    <t>xdmDocumentEntry.practiceSetting</t>
+  </si>
+  <si>
+    <t>Contexte de l’acte qui a engendré la création du document.</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J04-XdsPracticeSettingCode-CISIS/FHIR/JDV-J04-XdsPracticeSettingCode-CISIS|20240927120000</t>
+  </si>
+  <si>
+    <t>xdmDocumentEntry.type</t>
+  </si>
+  <si>
+    <t>Métadonnée représentant le type du document.</t>
+  </si>
+  <si>
+    <t>**Type Code**</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J07-XdsTypeCode-CISIS/FHIR/JDV-J07-XdsTypeCode-CISIS|20260629120000</t>
+  </si>
+  <si>
+    <t>xdmDocumentEntry.referenceIdList</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/xdmreferenceId
 </t>
   </si>
   <si>
-    <t>Cette métadonnée contient les codes, libellés et codes système représentant :  -un évènement documenté (acte, traitement, diagnostic, etc…), -une modalité d'acquisition (contexte imagerie), -une région anatomique (contexte imagerie).</t>
-  </si>
-  <si>
-    <t>xdmDocumentEntry.format</t>
-  </si>
-  <si>
-    <t>Métadonnée contenant les informations définissant le format du document.</t>
-  </si>
-  <si>
-    <t>**Format Code**</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J10-XdsFormatCode-CISIS/FHIR/JDV-J10-XdsFormatCode-CISIS|20260629120000</t>
-  </si>
-  <si>
-    <t>xdmDocumentEntry.healthcareFacilityTypeCode</t>
-  </si>
-  <si>
-    <t>Secteur d'activité lié à la prise en charge de la personne, en lien avec le document produit.</t>
-  </si>
-  <si>
-    <t>Healthcare Facility Type Code**</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J02-XdsHealthcareFacilityTypeCode-CISIS/FHIR/JDV-J02-XdsHealthcareFacilityTypeCode-CISIS|20260223120000</t>
-  </si>
-  <si>
-    <t>xdmDocumentEntry.practiceSetting</t>
-  </si>
-  <si>
-    <t>Contexte de l’acte qui a engendré la création du document.</t>
-  </si>
-  <si>
-    <t>**Practice Setting**</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J04-XdsPracticeSettingCode-CISIS/FHIR/JDV-J04-XdsPracticeSettingCode-CISIS|20240927120000</t>
-  </si>
-  <si>
-    <t>xdmDocumentEntry.type</t>
-  </si>
-  <si>
-    <t>Métadonnée représentant le type du document.</t>
-  </si>
-  <si>
-    <t>**Type Code**</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J07-XdsTypeCode-CISIS/FHIR/JDV-J07-XdsTypeCode-CISIS|20260629120000</t>
-  </si>
-  <si>
-    <t>xdmDocumentEntry.documentAvailability</t>
-  </si>
-  <si>
-    <t>Cette métadonnée représente '’accessibilité du document en indiquant si celui-ci est accessible en ligne ou non</t>
-  </si>
-  <si>
-    <t>xdmDocumentEntry.homeCommunityId</t>
-  </si>
-  <si>
-    <t>Cette métadonnée correspond à l'identifiant de la communauté représentée par le système cible, si celui-ci offre les fonctionnalités de communication avec d'autres communautés, présentées dans le profil XCA d'IHE. Elle n'est pas utilisée par les transactions décrites dans ce volet.</t>
-  </si>
-  <si>
-    <t>xdmDocumentEntry.creationTime</t>
-  </si>
-  <si>
-    <t>Cette métadonnée représente la date et l’heure de la création du document.</t>
-  </si>
-  <si>
-    <t>xdmDocumentEntry.referenceIdList</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base
-</t>
-  </si>
-  <si>
-    <t>Cette métadonnée contient une liste d'un ou plusieurs identifiant(s) d'objet(s) associé(s) au document.</t>
-  </si>
-  <si>
-    <t>xdmDocumentEntry.referenceIdList.CX1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {elementdefinition-identifier|5.3.0}
-</t>
-  </si>
-  <si>
-    <t>Identifiant de l'objet référencé</t>
-  </si>
-  <si>
-    <t>xdmDocumentEntry.referenceIdList.CX4</t>
-  </si>
-  <si>
-    <t>Identifiant de l’organisme ayant attribué l’identifiant de l'objet référencé</t>
-  </si>
-  <si>
-    <t>xdmDocumentEntry.referenceIdList.CX5</t>
-  </si>
-  <si>
-    <t>Type d’identifiant</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J197-XdsTypesIdentifiantsReferenceId-CISIS/FHIR/JDV-J197-XdsTypesIdentifiantsReferenceId-CISIS|20220624120000</t>
+    <t>Cette métadonnée contient une liste d'un ou plusieurs identifiant(s) d'objet(s) associé(s) au document. Liste d'éléments de type CX du standard HL7 v2.5.</t>
   </si>
 </sst>
 </file>
@@ -901,7 +900,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK35"/>
+  <dimension ref="A1:AK38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true" bestFit="true"/>
@@ -929,7 +928,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="121.359375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="117.46484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -1802,10 +1801,10 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s" s="2">
         <v>104</v>
@@ -1893,7 +1892,7 @@
         <v>81</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>74</v>
@@ -1905,10 +1904,10 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="L10" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="M10" t="s" s="2">
         <v>107</v>
@@ -1968,7 +1967,7 @@
         <v>81</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>74</v>
@@ -1996,7 +1995,7 @@
         <v>81</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>74</v>
@@ -2014,7 +2013,7 @@
         <v>110</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2071,7 +2070,7 @@
         <v>81</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>74</v>
@@ -2085,10 +2084,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2111,10 +2110,10 @@
         <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="M12" t="s" s="2">
         <v>114</v>
@@ -2168,7 +2167,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -2302,7 +2301,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>81</v>
@@ -2317,7 +2316,7 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>119</v>
@@ -2377,7 +2376,7 @@
         <v>118</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>81</v>
@@ -2405,7 +2404,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>81</v>
@@ -2420,13 +2419,13 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L15" t="s" s="2">
-        <v>122</v>
-      </c>
       <c r="M15" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2480,7 +2479,7 @@
         <v>120</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>81</v>
@@ -2497,10 +2496,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2523,13 +2522,13 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="L16" t="s" s="2">
-        <v>125</v>
-      </c>
       <c r="M16" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2580,7 +2579,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -2600,10 +2599,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2626,13 +2625,13 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L17" t="s" s="2">
-        <v>128</v>
-      </c>
       <c r="M17" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2683,7 +2682,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -2703,10 +2702,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2729,7 +2728,7 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>130</v>
@@ -2786,7 +2785,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -2935,13 +2934,13 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="L20" t="s" s="2">
-        <v>135</v>
-      </c>
       <c r="M20" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3012,10 +3011,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3023,7 +3022,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>81</v>
@@ -3038,13 +3037,13 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3095,10 +3094,10 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>81</v>
@@ -3115,10 +3114,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3126,7 +3125,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>81</v>
@@ -3141,13 +3140,13 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3174,11 +3173,13 @@
         <v>74</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="Y22" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>142</v>
+        <v>74</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>74</v>
@@ -3196,10 +3197,10 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>81</v>
@@ -3211,15 +3212,15 @@
         <v>74</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>143</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3230,7 +3231,7 @@
         <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>145</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>74</v>
@@ -3242,13 +3243,13 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3275,11 +3276,13 @@
         <v>74</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="Y23" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z23" t="s" s="2">
-        <v>148</v>
+        <v>74</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>74</v>
@@ -3297,13 +3300,13 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>145</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>74</v>
@@ -3317,10 +3320,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3328,10 +3331,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>74</v>
@@ -3343,13 +3346,13 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3400,13 +3403,13 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>74</v>
@@ -3420,10 +3423,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3446,13 +3449,13 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>91</v>
+        <v>146</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3483,7 +3486,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>74</v>
@@ -3501,7 +3504,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -3516,15 +3519,15 @@
         <v>74</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3550,10 +3553,10 @@
         <v>91</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3580,11 +3583,13 @@
         <v>74</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>159</v>
+        <v>74</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>74</v>
@@ -3602,7 +3607,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -3622,10 +3627,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3648,13 +3653,13 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3681,11 +3686,13 @@
         <v>74</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>163</v>
+        <v>74</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>74</v>
@@ -3703,7 +3710,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -3723,10 +3730,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3749,13 +3756,13 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3782,11 +3789,13 @@
         <v>74</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>167</v>
+        <v>74</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>74</v>
@@ -3804,7 +3813,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -3824,10 +3833,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3835,10 +3844,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>74</v>
@@ -3850,13 +3859,13 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>88</v>
+        <v>146</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3883,13 +3892,11 @@
         <v>74</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>74</v>
+        <v>165</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>74</v>
@@ -3907,13 +3914,13 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>74</v>
@@ -3927,10 +3934,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3941,7 +3948,7 @@
         <v>75</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>74</v>
@@ -3953,13 +3960,13 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4010,13 +4017,13 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>74</v>
@@ -4030,10 +4037,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4056,13 +4063,13 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4089,13 +4096,11 @@
         <v>74</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>74</v>
+        <v>170</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>74</v>
@@ -4113,7 +4118,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -4133,10 +4138,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4144,10 +4149,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>74</v>
@@ -4159,13 +4164,13 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>175</v>
+        <v>91</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4216,13 +4221,13 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>74</v>
@@ -4236,10 +4241,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4262,13 +4267,13 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>178</v>
+        <v>88</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4319,7 +4324,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -4339,10 +4344,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4365,13 +4370,13 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>178</v>
+        <v>116</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4422,7 +4427,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -4442,10 +4447,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4468,13 +4473,13 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>91</v>
+        <v>146</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4505,39 +4510,344 @@
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="Y36" s="2"/>
+      <c r="Z36" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="AA35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK35" t="s" s="2">
+      <c r="M37" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="Y37" s="2"/>
+      <c r="Z37" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK38" t="s" s="2">
         <v>74</v>
       </c>
     </row>
